--- a/Submission/Table 2.xlsx
+++ b/Submission/Table 2.xlsx
@@ -119,6 +119,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -381,6 +382,7 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="9.08"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
